--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104665_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104665_W23.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9919</v>
+        <v>1.7238</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4602</v>
+        <v>1.209</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5317</v>
+        <v>0.5148</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7917</v>
+        <v>-0.7952</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8744</v>
+        <v>-0.8786</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0835</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2073</v>
+        <v>0.1941</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4644</v>
+        <v>-0.4761</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.999</v>
+        <v>-0.9893</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>0.33</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1603</v>
+        <v>-0.0746</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1697</v>
+        <v>0.1383</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4406</v>
+        <v>0.8294</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4742</v>
+        <v>-0.1334</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9147999999999999</v>
+        <v>0.9628</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6931</v>
+        <v>1.6993</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3043</v>
+        <v>0.3126</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3887</v>
+        <v>1.3867</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4202</v>
+        <v>2.4149</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L3" t="n">
-        <v>2.351</v>
+        <v>2.3459</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7272</v>
+        <v>-0.7155</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3451</v>
+        <v>0.0406</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6261</v>
+        <v>-0.272</v>
       </c>
       <c r="U3" t="n">
-        <v>0.281</v>
+        <v>0.3126</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2479</v>
+        <v>-0.4639</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4296</v>
+        <v>2.0038</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.6775</v>
+        <v>-2.4678</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9216</v>
+        <v>-1.8807</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.87</v>
+        <v>-0.1691</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9485</v>
+        <v>-1.7116</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6008</v>
+        <v>1.7742</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.3893</v>
+        <v>1.4544</v>
       </c>
       <c r="L4" t="n">
-        <v>3.9902</v>
+        <v>0.3198</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.5224</v>
+        <v>-3.6549</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4807</v>
+        <v>-1.6235</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.0417</v>
+        <v>-2.0314</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6587</v>
+        <v>-0.8108</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0556</v>
+        <v>-0.6322</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3968</v>
+        <v>-0.1786</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.7997</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2831</v>
+        <v>-0.5155</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2751</v>
+        <v>-0.4834</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.5582</v>
+        <v>-0.0321</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.8742</v>
+        <v>-1.1452</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.163</v>
+        <v>0.1491</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.7113</v>
+        <v>-1.2943</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8055</v>
+        <v>0.1439</v>
       </c>
       <c r="K5" t="n">
-        <v>1.475</v>
+        <v>0.1067</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3304</v>
+        <v>0.0372</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.6797</v>
+        <v>-1.2891</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.638</v>
+        <v>0.0424</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.0417</v>
+        <v>-1.3315</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6357</v>
+        <v>-0.0743</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3962</v>
+        <v>-0.5786</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2395</v>
+        <v>0.5043</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>0.9317</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5782</v>
+        <v>-1.2826</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5857</v>
+        <v>-1.6869</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0075</v>
+        <v>0.4043</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1539</v>
+        <v>-1.9225</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1442</v>
+        <v>0.327</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2981</v>
+        <v>-2.2495</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1514</v>
+        <v>-1.4359</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1141</v>
+        <v>0.0689</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0373</v>
+        <v>-1.5048</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3053</v>
+        <v>-0.4866</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0301</v>
+        <v>0.2581</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3354</v>
+        <v>-0.7447</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1294</v>
+        <v>-0.043</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6956</v>
+        <v>-0.251</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5662</v>
+        <v>0.208</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4914</v>
+        <v>-1.3528</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9157</v>
+        <v>2.224</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4243</v>
+        <v>-3.5768</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9242</v>
+        <v>-0.924</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3202</v>
+        <v>-2.8693</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.2444</v>
+        <v>1.9453</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4288</v>
+        <v>2.573</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0693</v>
+        <v>-1.4037</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4981</v>
+        <v>3.9767</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4954</v>
+        <v>-3.497</v>
       </c>
       <c r="N7" t="n">
-        <v>0.251</v>
+        <v>-1.4656</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7463</v>
+        <v>-2.0314</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6805</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2477</v>
+        <v>-0.4579</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4869</v>
+        <v>-0.1214</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2392</v>
+        <v>-0.3366</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6914</v>
+        <v>-1.5475</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6723</v>
+        <v>1.1418</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0191</v>
+        <v>-2.6892</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6308</v>
+        <v>-4.0757</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1155</v>
+        <v>-1.7889</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7463</v>
+        <v>-2.2868</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4818</v>
+        <v>0.0225</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4818</v>
+        <v>-0.6248</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.6473</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.149</v>
+        <v>-4.0982</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5973000000000001</v>
+        <v>-1.1642</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7463</v>
+        <v>-2.934</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2268</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1948</v>
+        <v>-0.3823</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1905</v>
+        <v>-0.832</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0042</v>
+        <v>0.4498</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7283</v>
+        <v>-1.5668</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7187</v>
+        <v>-0.6839</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.447</v>
+        <v>-0.8829</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.0637</v>
+        <v>-0.6353</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7819</v>
+        <v>0.1095</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2817</v>
+        <v>-0.7447</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06370000000000001</v>
+        <v>-0.4934</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5999</v>
+        <v>-0.4934</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6636</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.1274</v>
+        <v>-0.1419</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1821</v>
+        <v>0.6028</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.9453</v>
+        <v>-0.7447</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0415</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5719</v>
+        <v>-0.0697</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3035</v>
+        <v>-0.1906</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7316</v>
+        <v>0.1209</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5151</v>
+        <v>-3.6124</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0277</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4874</v>
+        <v>-2.9194</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.3342</v>
+        <v>-2.4473</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7517</v>
+        <v>0.9848</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.5825</v>
+        <v>-3.4321</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.1862</v>
+        <v>1.7812</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9391</v>
+        <v>2.8096</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2471</v>
+        <v>-1.0284</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.148</v>
+        <v>-4.2285</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1874</v>
+        <v>-1.8248</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3354</v>
+        <v>-2.4037</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2048</v>
+        <v>-1.3927</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0393</v>
+        <v>-1.1084</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1654</v>
+        <v>-0.2843</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0608</v>
+        <v>-3.6672</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0148</v>
+        <v>-3.2991</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0459</v>
+        <v>-0.3681</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.4509</v>
+        <v>-4.3439</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9797</v>
+        <v>-0.7552</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.4305</v>
+        <v>-3.5888</v>
       </c>
       <c r="J11" t="n">
-        <v>1.807</v>
+        <v>-3.2127</v>
       </c>
       <c r="K11" t="n">
-        <v>2.8226</v>
+        <v>-0.9555</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.0157</v>
+        <v>-2.2572</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.2578</v>
+        <v>-1.1312</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8429</v>
+        <v>0.2003</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.4149</v>
+        <v>-1.3315</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8367</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4608</v>
+        <v>-0.1955</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3759</v>
+        <v>0.2592</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1875</v>
+        <v>-4.1851</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7094</v>
+        <v>-1.7167</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.478</v>
+        <v>-2.4684</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7057</v>
+        <v>-1.7088</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2712</v>
+        <v>-1.2723</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4345</v>
+        <v>-0.4365</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5008</v>
+        <v>-1.5076</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7517</v>
+        <v>-0.7552</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5232</v>
+        <v>-0.525</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3145</v>
+        <v>-0.3159</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.6244</v>
+        <v>-4.3383</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4877</v>
+        <v>-2.1679</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1366</v>
+        <v>-2.1704</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.4848</v>
+        <v>-3.4879</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.5469</v>
+        <v>-1.5453</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.9379</v>
+        <v>-1.9427</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0377</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1038</v>
+        <v>0.0887</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.5224</v>
+        <v>-3.497</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4807</v>
+        <v>-1.4656</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.0417</v>
+        <v>-2.0314</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1396</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1644</v>
+        <v>-0.8111</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0248</v>
+        <v>-0.0392</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-19.9756</v>
+        <v>-19.9789</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.003899999999999</v>
+        <v>-4.2857</v>
       </c>
       <c r="F14" t="n">
-        <v>-15.9714</v>
+        <v>-15.6932</v>
       </c>
       <c r="G14" t="n">
-        <v>-21.6426</v>
+        <v>-21.6672</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.395200000000001</v>
+        <v>-7.395700000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-14.2474</v>
+        <v>-14.2715</v>
       </c>
       <c r="J14" t="n">
-        <v>2.496</v>
+        <v>2.2632</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1420999999999998</v>
+        <v>-0.2799000000000003</v>
       </c>
       <c r="L14" t="n">
-        <v>2.638100000000001</v>
+        <v>2.543100000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-24.1386</v>
+        <v>-23.9304</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.252899999999999</v>
+        <v>-7.116</v>
       </c>
       <c r="O14" t="n">
-        <v>-16.8855</v>
+        <v>-16.8144</v>
       </c>
       <c r="P14" t="n">
-        <v>6.805099999999999</v>
+        <v>6.8291</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.9391</v>
+        <v>-7.9671</v>
       </c>
       <c r="R14" t="n">
-        <v>14.744</v>
+        <v>14.796</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.4306</v>
+        <v>-4.438</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.277500000000002</v>
+        <v>-5.2765</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8469999999999999</v>
+        <v>0.8384999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7068999999999999</v>
+        <v>-0.7024000000000006</v>
       </c>
       <c r="W14" t="n">
-        <v>6.7168</v>
+        <v>6.6946</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.423799999999999</v>
+        <v>-7.3972</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.1278</v>
+        <v>7.4775</v>
       </c>
       <c r="E15" t="n">
-        <v>7.6908</v>
+        <v>7.8906</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.4131</v>
       </c>
       <c r="G15" t="n">
-        <v>9.011100000000001</v>
+        <v>8.998799999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>3.075</v>
+        <v>3.0705</v>
       </c>
       <c r="I15" t="n">
-        <v>5.9361</v>
+        <v>5.9283</v>
       </c>
       <c r="J15" t="n">
-        <v>9.2423</v>
+        <v>9.210100000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0131</v>
+        <v>2.9992</v>
       </c>
       <c r="L15" t="n">
-        <v>6.2292</v>
+        <v>6.2109</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2312</v>
+        <v>-0.2113</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1101</v>
+        <v>0.251</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4174</v>
+        <v>-0.1813</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3073</v>
+        <v>0.4324</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.9439</v>
+        <v>5.2385</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3573</v>
+        <v>4.215</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5866</v>
+        <v>1.0235</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6778</v>
+        <v>2.689</v>
       </c>
       <c r="H16" t="n">
-        <v>1.489</v>
+        <v>1.4987</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1888</v>
+        <v>1.1903</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1458</v>
+        <v>3.1304</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5066</v>
+        <v>1.4996</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6392</v>
+        <v>1.6308</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.468</v>
+        <v>-0.4414</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0176</v>
+        <v>-0.0009</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3076</v>
+        <v>0.5982</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1603</v>
+        <v>0.0439</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1473</v>
+        <v>0.5543</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. TAVARES</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0869</v>
+        <v>2.5217</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6877</v>
+        <v>0.9487</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3992</v>
+        <v>1.5731</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2636</v>
+        <v>1.4239</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1009</v>
+        <v>1.7321</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1627</v>
+        <v>-0.3082</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5107</v>
+        <v>1.6653</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2122</v>
+        <v>1.7474</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2985</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2471</v>
+        <v>-0.2414</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1113</v>
+        <v>-0.0154</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1359</v>
+        <v>-0.226</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6805</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>2.0748</v>
+        <v>0.6505</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0162</v>
+        <v>-0.0258</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0585</v>
+        <v>0.6763</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9320000000000001</v>
+        <v>2.7237</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1607</v>
+        <v>2.7237</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4343</v>
+        <v>2.0404</v>
       </c>
       <c r="E18" t="n">
-        <v>1.112</v>
+        <v>0.6685</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3223</v>
+        <v>1.372</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4241</v>
+        <v>1.4097</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7359</v>
+        <v>-1.1288</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3118</v>
+        <v>2.5385</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6921</v>
+        <v>1.8511</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7694</v>
+        <v>-1.1279</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.07729999999999999</v>
+        <v>2.9789</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.268</v>
+        <v>-0.4414</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0335</v>
+        <v>-0.0009</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2345</v>
+        <v>-0.4405</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5468</v>
+        <v>0.7493</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0907</v>
+        <v>-0.1535</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4561</v>
+        <v>0.9028</v>
       </c>
       <c r="V18" t="n">
-        <v>2.7317</v>
+        <v>1.2472</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7317</v>
+        <v>1.2472</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>E. TAVARES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7926</v>
+        <v>1.8501</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2321</v>
+        <v>1.7363</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5605</v>
+        <v>0.1137</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4051</v>
+        <v>1.2788</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1299</v>
+        <v>1.1055</v>
       </c>
       <c r="I19" t="n">
-        <v>2.5349</v>
+        <v>0.1733</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8731</v>
+        <v>1.5045</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1123</v>
+        <v>1.2066</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9853</v>
+        <v>0.2979</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.468</v>
+        <v>-0.2257</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0176</v>
+        <v>-0.1011</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4504</v>
+        <v>-0.1246</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4951</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6261</v>
+        <v>0.0741</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1211</v>
+        <v>0.746</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2534</v>
+        <v>-0.9317</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2534</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4402</v>
+        <v>1.6567</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1726</v>
+        <v>1.2681</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7324000000000001</v>
+        <v>0.3886</v>
       </c>
       <c r="G20" t="n">
-        <v>1.9041</v>
+        <v>1.0724</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5815</v>
+        <v>0.3187</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3225</v>
+        <v>0.7537</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2422</v>
+        <v>1.2403</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6451</v>
+        <v>-0.4277</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5971</v>
+        <v>1.668</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3381</v>
+        <v>-0.168</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0636</v>
+        <v>0.7463</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2745</v>
+        <v>-0.9143</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6288</v>
+        <v>0.129</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0696</v>
+        <v>0.0278</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6983</v>
+        <v>0.1013</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.073</v>
+        <v>1.3994</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0452</v>
+        <v>2.4005</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0279</v>
+        <v>-1.0011</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0703</v>
+        <v>1.9046</v>
       </c>
       <c r="H21" t="n">
-        <v>0.316</v>
+        <v>1.5797</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7543</v>
+        <v>0.3248</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2538</v>
+        <v>2.2333</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4227</v>
+        <v>1.6375</v>
       </c>
       <c r="L21" t="n">
-        <v>1.6765</v>
+        <v>0.5958</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1835</v>
+        <v>-0.3287</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7387</v>
+        <v>-0.0578</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9222</v>
+        <v>-0.271</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4509</v>
+        <v>0.5843</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2087</v>
+        <v>0.1672</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2423</v>
+        <v>0.4171</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2171</v>
+        <v>-0.821</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4507</v>
+        <v>1.5231</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7411</v>
+        <v>0.4187</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7358</v>
+        <v>0.7179</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0053</v>
+        <v>-0.2992</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8270999999999999</v>
+        <v>0.5891</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9391</v>
+        <v>1.1926</v>
       </c>
       <c r="L22" t="n">
-        <v>0.112</v>
+        <v>-0.6035</v>
       </c>
       <c r="M22" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.1704</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2033</v>
+        <v>-0.4747</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1172</v>
+        <v>0.3043</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>1.7965</v>
+        <v>0.2834</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0858</v>
+        <v>-0.272</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7107</v>
+        <v>0.5554</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1295</v>
+        <v>-0.1955</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1549</v>
+        <v>-0.2718</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0254</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4118</v>
+        <v>0.9124</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7157</v>
+        <v>-0.1123</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3038</v>
+        <v>1.0247</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6052999999999999</v>
+        <v>1.0267</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2051</v>
+        <v>0.1034</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5998</v>
+        <v>0.9233</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1935</v>
+        <v>-0.1143</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4894</v>
+        <v>-0.2157</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2959</v>
+        <v>0.1014</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5414</v>
+        <v>0.0302</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6261</v>
+        <v>-0.1604</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0847</v>
+        <v>0.1906</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.31</v>
+        <v>-0.4282</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3783</v>
+        <v>-0.7487</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0683</v>
+        <v>0.3205</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9119</v>
+        <v>-0.742</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.117</v>
+        <v>-0.7407</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0289</v>
+        <v>-0.0013</v>
       </c>
       <c r="J24" t="n">
-        <v>1.0341</v>
+        <v>-0.8438</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1039</v>
+        <v>-0.9555</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9302</v>
+        <v>0.1117</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1222</v>
+        <v>0.1018</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2209</v>
+        <v>0.2148</v>
       </c>
       <c r="O24" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.113</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0877</v>
+        <v>0.6992</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2782</v>
+        <v>0.1438</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1905</v>
+        <v>0.5554</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.9195</v>
+        <v>-0.5779</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.3356</v>
+        <v>-0.453</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4161</v>
+        <v>-0.1249</v>
       </c>
       <c r="G25" t="n">
-        <v>1.3884</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.3678</v>
+        <v>0.7323</v>
       </c>
       <c r="I25" t="n">
-        <v>2.7561</v>
+        <v>0.1925</v>
       </c>
       <c r="J25" t="n">
-        <v>1.4196</v>
+        <v>0.9361</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.4138</v>
+        <v>0.6755</v>
       </c>
       <c r="L25" t="n">
-        <v>2.8334</v>
+        <v>0.2607</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0312</v>
+        <v>-0.0113</v>
       </c>
       <c r="N25" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.5878</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3726</v>
+        <v>0.0419</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4869</v>
+        <v>-0.251</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8595</v>
+        <v>0.2929</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.232</v>
+        <v>-0.9163</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6743</v>
+        <v>-1.1399</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5577</v>
+        <v>0.2236</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9156</v>
+        <v>1.3762</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7316</v>
+        <v>-1.378</v>
       </c>
       <c r="I26" t="n">
-        <v>0.184</v>
+        <v>2.7542</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9468</v>
+        <v>1.3874</v>
       </c>
       <c r="K26" t="n">
-        <v>0.6856</v>
+        <v>-1.4349</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2612</v>
+        <v>2.8223</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0312</v>
+        <v>-0.0113</v>
       </c>
       <c r="N26" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.4537</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R26" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6012999999999999</v>
+        <v>0.3904</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4869</v>
+        <v>-0.251</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1143</v>
+        <v>0.6415</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>19.9755</v>
+        <v>20.7685</v>
       </c>
       <c r="E27" t="n">
-        <v>15.9717</v>
+        <v>15.6933</v>
       </c>
       <c r="F27" t="n">
-        <v>4.003900000000001</v>
+        <v>5.0753</v>
       </c>
       <c r="G27" t="n">
-        <v>21.6427</v>
+        <v>21.6674</v>
       </c>
       <c r="H27" t="n">
-        <v>7.395099999999998</v>
+        <v>7.395600000000002</v>
       </c>
       <c r="I27" t="n">
-        <v>14.2474</v>
+        <v>14.2716</v>
       </c>
       <c r="J27" t="n">
-        <v>24.1387</v>
+        <v>23.9305</v>
       </c>
       <c r="K27" t="n">
-        <v>7.2531</v>
+        <v>7.115800000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>16.8855</v>
+        <v>16.8147</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.496</v>
+        <v>-2.2634</v>
       </c>
       <c r="N27" t="n">
-        <v>0.142</v>
+        <v>0.2795</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.638100000000001</v>
+        <v>-2.543</v>
       </c>
       <c r="P27" t="n">
-        <v>-6.8049</v>
+        <v>-6.8289</v>
       </c>
       <c r="Q27" t="n">
-        <v>-14.7443</v>
+        <v>-14.7963</v>
       </c>
       <c r="R27" t="n">
-        <v>7.9392</v>
+        <v>7.9672</v>
       </c>
       <c r="S27" t="n">
-        <v>4.4308</v>
+        <v>5.227499999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.8468999999999999</v>
+        <v>-0.8381999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>5.277399999999999</v>
+        <v>6.066</v>
       </c>
       <c r="V27" t="n">
-        <v>0.7068999999999996</v>
+        <v>0.702300000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>7.4238</v>
+        <v>7.397100000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.716899999999999</v>
+        <v>-6.6947</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104665_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104665_W23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.3972</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104665_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-6.6947</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
